--- a/output/laminas_comunales/comunal_o_ocup_a_2023_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2023_los_rios.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,91 +375,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Río Bueno</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="C2">
-        <v>42.0616914462251</v>
+        <v>56.9167447363048</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Río Bueno</t>
         </is>
       </c>
       <c r="C3">
-        <v>37.5427758042301</v>
+        <v>56.7557803468208</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C4">
-        <v>33.1556679177092</v>
+        <v>56.7421631573978</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Máfil</t>
         </is>
       </c>
       <c r="C5">
-        <v>33.1212283319725</v>
+        <v>53.910587784798</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C6">
-        <v>33.0196259861693</v>
+        <v>53.6046718850672</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Máfil</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="C7">
-        <v>32.7319839640168</v>
+        <v>53.4232519961197</v>
       </c>
     </row>
     <row r="8">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>32.0306748466258</v>
+        <v>52.5377833753149</v>
       </c>
     </row>
     <row r="9">
@@ -489,67 +489,1357 @@
         </is>
       </c>
       <c r="C9">
-        <v>31.5647576170035</v>
+        <v>52.1855882771376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Futrono</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="C10">
-        <v>29.0347904665085</v>
+        <v>51.9536193368767</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C11">
-        <v>27.7391729046983</v>
+        <v>51.3713300335937</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corral</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="C12">
-        <v>27.6240892531876</v>
+        <v>51.290234026491</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>48.6863217007621</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>48.3173928444917</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>47.8724658180104</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>46.0808967470532</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>45.8485845775138</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>44.8106060606061</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>44.2856509793495</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>43.5533095521205</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>43.0470571095571</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>42.8974780701754</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>14203</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Lago Ranco</t>
         </is>
       </c>
-      <c r="C13">
+      <c r="C23">
+        <v>42.6547275970907</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>42.0779759435919</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>42.0616914462251</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>41.8753429199444</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>40.7337419135172</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>40.6120317504526</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>40.147521780511</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>39.8514416315049</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>39.0203303274185</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>39.0154968094804</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>38.8864734299517</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>38.735766827892</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>38.5300024631009</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>37.9765153394526</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>37.5427758042301</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>37.4924347452056</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>37.2764399380369</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>37.1986522399393</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>36.4457019671248</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>35.0719551963703</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>34.6632305997222</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>34.587759353315</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>34.3307055263577</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>33.7302127273552</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>33.4771455223881</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>33.1556679177092</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>33.1212283319725</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>33.1071130869686</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>33.0196259861693</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>32.7656927505453</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>32.7319839640168</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>32.153965785381</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>32.0306748466258</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>31.5647576170035</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>31.4142992150283</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>30.5763847778582</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>29.7425621028307</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>29.5683100318862</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>29.483355782182</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>29.463755828741</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>29.3863749688357</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>29.0347904665085</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>29.0208232053152</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>28.7297435341825</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>28.0700782749963</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>27.8123372759057</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>27.7391729046983</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>27.6240892531876</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>27.2201569599339</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>26.964908847797</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>26.4276524148852</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>26.2118637209679</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>25.9514912462805</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C76">
         <v>25.4992809047526</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>25.3218618469918</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>25.2581434958484</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>25.1277139208174</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>24.3755063462058</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>24.0426584414829</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>23.984988058683</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>23.2244520352975</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>22.0418149466192</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>21.3590615210291</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>14.7259062776304</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>10.9399630064966</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>10.4514902272928</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>10.4480834294397</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>10.3797135724609</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>10.04759605772</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>9.598434575463671</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>9.487382895134481</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>9.276997976732421</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>8.855</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>8.604977216964601</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>8.323813875561649</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>7.09808259587021</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>6.87337123904288</v>
       </c>
     </row>
   </sheetData>
